--- a/GRAMMAR/8_18_12.xlsx
+++ b/GRAMMAR/8_18_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE7DC8E-1E81-48F7-AF81-2BDC1BC12EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D74F22B-02FD-4ACB-99DE-6676CDFC8046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="960" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="1560" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>Fre</t>
   </si>
@@ -448,6 +448,14 @@
   </si>
   <si>
     <t>"たがる"否定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连用形+次第</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一…就…</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -840,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -1093,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -1104,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -1115,10 +1123,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
@@ -1126,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
@@ -1137,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
@@ -1148,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
@@ -1159,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
@@ -1170,13 +1178,10 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -1184,10 +1189,13 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
@@ -1195,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
@@ -1206,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
@@ -1217,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
@@ -1228,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
@@ -1239,13 +1247,10 @@
         <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
@@ -1253,10 +1258,13 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
@@ -1264,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
@@ -1275,10 +1283,10 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
@@ -1286,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
@@ -1297,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
@@ -1308,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
@@ -1319,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
@@ -1330,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
@@ -1341,10 +1349,10 @@
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
@@ -1352,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
@@ -1363,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
@@ -1374,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
@@ -1385,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
@@ -1396,9 +1404,20 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="2">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>94</v>
       </c>
     </row>
